--- a/all reports/Daily Booking Sheet & Route Plan (1).xlsx
+++ b/all reports/Daily Booking Sheet & Route Plan (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{556C56F8-E4F0-41A7-B2B0-35A069BE30DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B558973-4F53-40F5-B392-C735B96E576E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1154,6 +1154,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:M57"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -2229,6 +2232,6 @@
     <mergeCell ref="C1:J2"/>
   </mergeCells>
   <pageMargins left="0.2" right="0.2" top="0.25" bottom="0.25" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="48" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
--- a/all reports/Daily Booking Sheet & Route Plan (1).xlsx
+++ b/all reports/Daily Booking Sheet & Route Plan (1).xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B558973-4F53-40F5-B392-C735B96E576E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC73D0C9-C9B3-4307-A922-4744072E6DC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="4" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$M$29</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -807,14 +810,50 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -835,42 +874,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1174,81 +1177,81 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="53" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="46" t="s">
+      <c r="B1" s="54"/>
+      <c r="C1" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="46"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="48"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
+      <c r="I1" s="59"/>
+      <c r="J1" s="60"/>
       <c r="K1" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="43"/>
-      <c r="M1" s="42"/>
+      <c r="L1" s="42"/>
+      <c r="M1" s="54"/>
     </row>
     <row r="2" spans="1:13" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="41"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
+      <c r="A2" s="53"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="62"/>
       <c r="K2" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="44"/>
-      <c r="M2" s="45"/>
+      <c r="L2" s="56"/>
+      <c r="M2" s="57"/>
     </row>
     <row r="3" spans="1:13" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="53" t="s">
+      <c r="B3" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="55" t="s">
+      <c r="C3" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="53" t="s">
+      <c r="D3" s="44" t="s">
         <v>4</v>
       </c>
       <c r="E3" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="41" t="s">
+      <c r="F3" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="43"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="58" t="s">
+      <c r="G3" s="42"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="J3" s="43"/>
-      <c r="K3" s="59"/>
-      <c r="L3" s="53" t="s">
+      <c r="J3" s="42"/>
+      <c r="K3" s="43"/>
+      <c r="L3" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="M3" s="60" t="s">
+      <c r="M3" s="46" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="52"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="62"/>
-      <c r="D4" s="57"/>
+      <c r="A4" s="51"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="55"/>
       <c r="E4" s="40" t="s">
         <v>16</v>
       </c>
@@ -1270,8 +1273,8 @@
       <c r="K4" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="L4" s="54"/>
-      <c r="M4" s="61"/>
+      <c r="L4" s="45"/>
+      <c r="M4" s="47"/>
     </row>
     <row r="5" spans="1:13" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="12">
@@ -1702,42 +1705,42 @@
       <c r="A30" s="2"/>
     </row>
     <row r="31" spans="1:13" ht="20.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="51" t="s">
+      <c r="A31" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="B31" s="53" t="s">
+      <c r="B31" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="C31" s="55" t="s">
+      <c r="C31" s="48" t="s">
         <v>1</v>
       </c>
       <c r="D31" s="34"/>
-      <c r="E31" s="53" t="s">
+      <c r="E31" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="F31" s="41" t="s">
+      <c r="F31" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="G31" s="43"/>
-      <c r="H31" s="42"/>
-      <c r="I31" s="58" t="s">
+      <c r="G31" s="42"/>
+      <c r="H31" s="54"/>
+      <c r="I31" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="J31" s="43"/>
-      <c r="K31" s="59"/>
-      <c r="L31" s="53" t="s">
+      <c r="J31" s="42"/>
+      <c r="K31" s="43"/>
+      <c r="L31" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="M31" s="60" t="s">
+      <c r="M31" s="46" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="20.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="52"/>
-      <c r="B32" s="54"/>
-      <c r="C32" s="56"/>
+      <c r="A32" s="51"/>
+      <c r="B32" s="45"/>
+      <c r="C32" s="52"/>
       <c r="D32" s="35"/>
-      <c r="E32" s="54"/>
+      <c r="E32" s="45"/>
       <c r="F32" s="21" t="s">
         <v>12</v>
       </c>
@@ -1756,8 +1759,8 @@
       <c r="K32" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="L32" s="54"/>
-      <c r="M32" s="61"/>
+      <c r="L32" s="45"/>
+      <c r="M32" s="47"/>
     </row>
     <row r="33" spans="1:13" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="12">
@@ -2209,6 +2212,19 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="C1:J2"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="E31:E32"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="D3:D4"/>
     <mergeCell ref="I31:K31"/>
     <mergeCell ref="L31:L32"/>
     <mergeCell ref="M31:M32"/>
@@ -2217,21 +2233,8 @@
     <mergeCell ref="I3:K3"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="M3:M4"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="C31:C32"/>
-    <mergeCell ref="E31:E32"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="F31:H31"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="C1:J2"/>
   </mergeCells>
   <pageMargins left="0.2" right="0.2" top="0.25" bottom="0.25" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="48" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="95" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>